--- a/Scenario_Observable_Behaviours.xlsx
+++ b/Scenario_Observable_Behaviours.xlsx
@@ -1116,16 +1116,56 @@
       <c r="B12" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Recognize the loss of automatic roll-out guidance after touchdown and take over manual directional control promptly, particularly relevant during low-visibility autoland operations.</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Promptly recognizes the ROLL OUT FAULT indication and understands automatic directional guidance is no longer available after touchdown.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>APK</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Takes over manual directional control without delay (rudder pedal steering, transitioning to tiller as speed reduces), maintaining runway centerline.</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>FCOM_PRO</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Calls out the fault and the transition to manual control clearly to the other pilot.</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>EASA_EBT</t>
+        </is>
+      </c>
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="7" t="n"/>
@@ -1139,16 +1179,56 @@
       <c r="B13" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Recognize the loss of TCAS protection before any RA is generated, and compensate with increased visual scan and ATC coordination since automated traffic alerting is unavailable.</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Recognizes the TCAS fault/degraded status and understands the aircraft no longer has Resolution Advisory protection.</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Notifies ATC of the TCAS unserviceability per procedure.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>OM_A</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>WLM</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Increases visual traffic scan and requests additional traffic information from ATC to compensate for the loss of automated alerting.</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>EASA_EBT</t>
+        </is>
+      </c>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="7" t="n"/>
@@ -1275,16 +1355,56 @@
       <c r="B19" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Recognize the loss of the primary VHF radio, transfer communication to the backup radio without unnecessary delay, and do not reset the tripped circuit breaker in flight without following the correct procedure.</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>APK</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Follows the correct procedure without resetting the tripped circuit breaker in flight unless explicitly authorized to do so.</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Transfers communication to VHF 2 promptly and re-establishes contact with ATC without excessive delay.</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>FCOM_PRO</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>WLM</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Manages the fault (PM) while the other pilot (PF) continues to prioritize flight path monitoring, avoiding dual head-down time.</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>EASA_EBT</t>
+        </is>
+      </c>
       <c r="M19" s="7" t="n"/>
       <c r="N19" s="7" t="n"/>
       <c r="O19" s="7" t="n"/>
@@ -1372,16 +1492,56 @@
       <c r="B22" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Identify the door seal leak indication, monitor the cabin pressurization trend closely, and be prepared to descend if the leak becomes operationally significant.</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Monitors cabin altitude and differential pressure trend closely following the door leak indication rather than a one-time check.</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>APK</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Applies the correct procedure and any associated speed or altitude restriction for the affected door/seal.</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>FCOM_PRO</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Evaluates whether continued flight at the planned altitude remains appropriate or whether a lower level/diversion is warranted based on leak severity.</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>OM_A</t>
+        </is>
+      </c>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n"/>
       <c r="O22" s="7" t="n"/>
@@ -2216,16 +2376,56 @@
       <c r="B46" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
-      <c r="K46" s="7" t="n"/>
-      <c r="L46" s="7" t="n"/>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Direct immediate use of the approved lithium-battery fire containment procedure and assess the need for immediate diversion.</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Directs immediate use of the fire extinguisher, water, and containment bag/bin per procedure, and considers immediate diversion.</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Coordinates promptly with cabin crew for real-time fire status updates and gives clear, actionable instructions.</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>OM_A</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>WLM</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>Balances continued flying duties (PF) against decision-making/coordination duties (PM/Capt) without becoming fixated on the cabin event to the detriment of flight path control.</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>EASA_EBT</t>
+        </is>
+      </c>
       <c r="M46" s="7" t="n"/>
       <c r="N46" s="7" t="n"/>
       <c r="O46" s="7" t="n"/>
@@ -2847,16 +3047,56 @@
       <c r="B61" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
-      <c r="K61" s="7" t="n"/>
-      <c r="L61" s="7" t="n"/>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Recognize the alert reflects an uplock (not downlock) issue, recycle the gear if speed permits to close the door, and respect the resulting speed restriction and unreliable FMS predictions if it does not.</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Correctly identifies the alert as a landing gear door not fully uplocked rather than a downlock/gear-position problem, and monitors the WHEEL SD page during any recycle attempt.</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>FCOM_PRO</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>APK</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Recycles the landing gear (lever down, wait for downlock and door closure while monitoring the WHEEL page, then lever up) only when speed is below 220 kt/0.54, following the sequence without skipping the monitoring step.</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Accepts the MAX SPEED 250/0.60 restriction if the recycle is unsuccessful, and disregards FMS fuel predictions given the L/G DOOR INOP SYS status, applying the QRH/OPS Fuel Penalty Factor table instead.</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>FCOM_PRO</t>
+        </is>
+      </c>
       <c r="M61" s="7" t="n"/>
       <c r="N61" s="7" t="n"/>
       <c r="O61" s="7" t="n"/>
@@ -3302,16 +3542,56 @@
         </is>
       </c>
       <c r="B78" s="6" t="n"/>
-      <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
-      <c r="E78" s="7" t="n"/>
-      <c r="F78" s="7" t="n"/>
-      <c r="G78" s="7" t="n"/>
-      <c r="H78" s="7" t="n"/>
-      <c r="I78" s="7" t="n"/>
-      <c r="J78" s="7" t="n"/>
-      <c r="K78" s="7" t="n"/>
-      <c r="L78" s="7" t="n"/>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Reassess remaining holdover time and runway/wing contamination status as snowfall intensity changes, and delay, return for re-treatment, or reject as required.</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Recognizes the deteriorating precipitation intensity and its effect on remaining de-icing/anti-icing holdover time.</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>OM_A</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Makes a timely decision to return for re-treatment, delay departure, or reject the take-off if holdover time is exceeded or contamination is suspected.</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>Communicates the changed conditions and revised plan clearly to ATC, ground crew, and cabin crew as applicable.</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>EASA_EBT</t>
+        </is>
+      </c>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n"/>
       <c r="O78" s="7" t="n"/>
@@ -3344,16 +3624,56 @@
         </is>
       </c>
       <c r="B80" s="6" t="n"/>
-      <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
-      <c r="E80" s="7" t="n"/>
-      <c r="F80" s="7" t="n"/>
-      <c r="G80" s="7" t="n"/>
-      <c r="H80" s="7" t="n"/>
-      <c r="I80" s="7" t="n"/>
-      <c r="J80" s="7" t="n"/>
-      <c r="K80" s="7" t="n"/>
-      <c r="L80" s="7" t="n"/>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Assess a reported runway obstruction against take-off roll progress and available distance, and reject the take-off if required.</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Correctly assesses the reported obstruction's position relative to the take-off roll and remaining usable runway.</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>OM_A</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>Makes a timely and correct reject/continue decision based on speed regime (below/above V1) and obstruction risk.</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>Clearly communicates the rejected take-off (or continued departure) decision and reasoning to ATC and the other pilot.</t>
+        </is>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>FCOM_PRO</t>
+        </is>
+      </c>
       <c r="M80" s="7" t="n"/>
       <c r="N80" s="7" t="n"/>
       <c r="O80" s="7" t="n"/>
@@ -3613,16 +3933,56 @@
         </is>
       </c>
       <c r="B89" s="6" t="n"/>
-      <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="n"/>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
-      <c r="I89" s="7" t="n"/>
-      <c r="J89" s="7" t="n"/>
-      <c r="K89" s="7" t="n"/>
-      <c r="L89" s="7" t="n"/>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Reassess landing distance and go-around margins in light of a poor braking action report, and adjust technique or divert as necessary.</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Factors the braking action report into a reassessment of landing performance margins before continuing the approach.</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>OM_A</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Decides appropriately between continuing with adjusted technique, going around, or diverting.</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>APK</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>Applies the correct adjusted landing technique (e.g. autobrake MAX, full reverse) consistent with the reported braking action.</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>FCOM_PRO</t>
+        </is>
+      </c>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n"/>
       <c r="O89" s="7" t="n"/>
@@ -3655,16 +4015,56 @@
         </is>
       </c>
       <c r="B91" s="6" t="n"/>
-      <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
-      <c r="J91" s="7" t="n"/>
-      <c r="K91" s="7" t="n"/>
-      <c r="L91" s="7" t="n"/>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Assess the operational impact of a reduced Rescue and Fire Fighting Services category and decide whether dispatch or continuation remains appropriate.</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>KNO</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>Understands the operational and regulatory significance of the reduced RFFS category for the flight.</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>OM_A</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Makes an appropriate decision on whether to continue, delay, or divert given the reduced fire cover.</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>EASA_EBT</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>Communicates the RFFS status and the resulting decision clearly to the operator, ATC, and cabin crew as relevant.</t>
+        </is>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>OM_A</t>
+        </is>
+      </c>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n"/>
       <c r="O91" s="7" t="n"/>
@@ -3802,16 +4202,56 @@
         </is>
       </c>
       <c r="B98" s="6" t="n"/>
-      <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
-      <c r="E98" s="7" t="n"/>
-      <c r="F98" s="7" t="n"/>
-      <c r="G98" s="7" t="n"/>
-      <c r="H98" s="7" t="n"/>
-      <c r="I98" s="7" t="n"/>
-      <c r="J98" s="7" t="n"/>
-      <c r="K98" s="7" t="n"/>
-      <c r="L98" s="7" t="n"/>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Apply the correct substitute procedure for a missing mid-point RVR reading during a low-visibility approach and decide on continuation accordingly.</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>APK</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Correctly applies the regulatory substitution rule for the missing mid RVR reading (e.g. use of touchdown/rollout RVR).</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>OM_A</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Makes a sound continue/go-around decision based on the effective visibility assessment with the missing sensor.</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>Briefs the RVR limitation and its effect on approach minima to the other pilot before commencing the approach.</t>
+        </is>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>EASA_EBT</t>
+        </is>
+      </c>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n"/>
       <c r="O98" s="7" t="n"/>
@@ -4012,16 +4452,56 @@
         </is>
       </c>
       <c r="B108" s="6" t="n"/>
-      <c r="C108" s="7" t="n"/>
-      <c r="D108" s="7" t="n"/>
-      <c r="E108" s="7" t="n"/>
-      <c r="F108" s="7" t="n"/>
-      <c r="G108" s="7" t="n"/>
-      <c r="H108" s="7" t="n"/>
-      <c r="I108" s="7" t="n"/>
-      <c r="J108" s="7" t="n"/>
-      <c r="K108" s="7" t="n"/>
-      <c r="L108" s="7" t="n"/>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Comply immediately with the TCAS RA, then recognize and recover from any resulting upset using standard technique.</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>FPM</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Complies immediately and correctly with the TCAS RA guidance, with no maneuvering contrary to the RA.</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>Promptly recognizes a developing upset condition (unusual pitch/bank/airspeed trend) following the RA response.</t>
+        </is>
+      </c>
+      <c r="I108" s="7" t="inlineStr">
+        <is>
+          <t>EASA_EBT</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>FPM</t>
+        </is>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>Applies the correct upset recovery technique (unload, wings level, adjust thrust) to return to a stabilized flight path.</t>
+        </is>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>FCOM_PRO</t>
+        </is>
+      </c>
       <c r="M108" s="7" t="n"/>
       <c r="N108" s="7" t="n"/>
       <c r="O108" s="7" t="n"/>
@@ -4282,16 +4762,56 @@
       <c r="B118" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="C118" s="7" t="n"/>
-      <c r="D118" s="7" t="n"/>
-      <c r="E118" s="7" t="n"/>
-      <c r="F118" s="7" t="n"/>
-      <c r="G118" s="7" t="n"/>
-      <c r="H118" s="7" t="n"/>
-      <c r="I118" s="7" t="n"/>
-      <c r="J118" s="7" t="n"/>
-      <c r="K118" s="7" t="n"/>
-      <c r="L118" s="7" t="n"/>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Recognize unreliable airspeed indications from a partial pitot blockage and apply the pitch-and-thrust unreliable-speed technique while cross-checking standby instruments.</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>SAW</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>Recognizes discrepant airspeed/altitude indications and identifies a probable unreliable-airspeed condition rather than reacting to a single displayed value.</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>QRH</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>APK</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t>Applies the correct pitch attitude and thrust (N1/EPR) table for the phase of flight per the unreliable-airspeed procedure.</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="inlineStr">
+        <is>
+          <t>FCOM_PRO</t>
+        </is>
+      </c>
+      <c r="J118" s="7" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>Cross-checks and calls out standby instrument indications with the other pilot to confirm the safe flight path before further action.</t>
+        </is>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>EASA_EBT</t>
+        </is>
+      </c>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n"/>
       <c r="O118" s="7" t="n"/>
